--- a/out/07_Ops/SNX-OPS-FRM-07 Maintenance Schedule Service Report (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-FRM-07 Maintenance Schedule Service Report (Rev00 DRAFT).xlsx
@@ -14,7 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Report" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jadwal PM'!$5:$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Service Report'!$A$4:$P$155</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Service Report'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -183,7 +186,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -367,6 +370,48 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -768,8 +813,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="33">
-      <c r="A4" s="36" t="inlineStr">
+    <row r="3" s="33">
+      <c r="A3" s="62" t="n"/>
+      <c r="B3" s="62" t="n"/>
+      <c r="C3" s="62" t="n"/>
+      <c r="D3" s="62" t="n"/>
+      <c r="E3" s="62" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="33">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -779,9 +831,12 @@
           <t>SNX-OPS-FRM-07</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="33">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="C4" s="62" t="n"/>
+      <c r="D4" s="62" t="n"/>
+      <c r="E4" s="62" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="33">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -791,9 +846,12 @@
           <t>Maintenance Schedule &amp; Service Report</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="33">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="62" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="33">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -803,9 +861,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="33">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="C6" s="62" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="33">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -815,9 +876,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="33">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="C7" s="62" t="n"/>
+      <c r="D7" s="62" t="n"/>
+      <c r="E7" s="62" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="33">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -827,9 +891,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="33">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="C8" s="62" t="n"/>
+      <c r="D8" s="62" t="n"/>
+      <c r="E8" s="62" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="33">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -839,9 +906,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="33">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="C9" s="62" t="n"/>
+      <c r="D9" s="62" t="n"/>
+      <c r="E9" s="62" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="33">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -851,9 +921,12 @@
           <t>Lead NOC</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="33">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="C10" s="62" t="n"/>
+      <c r="D10" s="62" t="n"/>
+      <c r="E10" s="62" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="33">
+      <c r="A11" s="63" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -863,9 +936,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="33">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="C11" s="62" t="n"/>
+      <c r="D11" s="62" t="n"/>
+      <c r="E11" s="62" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="33">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -875,9 +951,12 @@
           <t>Klausul 7.1.3, 8.5.1</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="33">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="C12" s="62" t="n"/>
+      <c r="D12" s="62" t="n"/>
+      <c r="E12" s="62" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="33">
+      <c r="A13" s="63" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -887,9 +966,12 @@
           <t>Kontrol Annex A 7.13</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="33">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="C13" s="62" t="n"/>
+      <c r="D13" s="62" t="n"/>
+      <c r="E13" s="62" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="33">
+      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -899,140 +981,200 @@
           <t>3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="33">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="C14" s="62" t="n"/>
+      <c r="D14" s="62" t="n"/>
+      <c r="E14" s="62" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="33">
+      <c r="A15" s="63" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>Jadwal preventive maintenance tahunan dan service report untuk preventive maupun corrective maintenance sesuai SNX-OPS-SOP-03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="33">
-      <c r="A17" s="38" t="inlineStr">
+          <t>Jadwal preventive maintenance tahunan, serta service report untuk preventive dan corrective maintenance, sesuai SNX-OPS-SOP-03.</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="n"/>
+      <c r="D15" s="62" t="n"/>
+      <c r="E15" s="62" t="n"/>
+    </row>
+    <row r="16" s="33">
+      <c r="A16" s="62" t="n"/>
+      <c r="B16" s="62" t="n"/>
+      <c r="C16" s="62" t="n"/>
+      <c r="D16" s="62" t="n"/>
+      <c r="E16" s="62" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="33">
+      <c r="A17" s="64" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="33">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="B17" s="62" t="n"/>
+      <c r="C17" s="62" t="n"/>
+      <c r="D17" s="62" t="n"/>
+      <c r="E17" s="62" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="33">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="40" t="inlineStr">
         <is>
-          <t>Isi tahun di sheet Jadwal PM sel B3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="33">
-      <c r="A19" s="39" t="inlineStr">
+          <t>Isi tahun di sel B3 sheet Jadwal PM.</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="n"/>
+      <c r="D18" s="62" t="n"/>
+      <c r="E18" s="62" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="33">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>Per aktivitas, isi bulan dengan kode: R = rencana, S = selesai, T = tertunda. Kepatuhan dihitung otomatis (S dibagi R+S+T).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="33">
-      <c r="A20" s="39" t="inlineStr">
+          <t>Isi bulan untuk setiap aktivitas dengan kode R (rencana), S (selesai), atau T (tertunda). Kepatuhan dihitung otomatis: S dibagi R+S+T.</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="n"/>
+      <c r="D19" s="62" t="n"/>
+      <c r="E19" s="62" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="33">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>Setiap pelaksanaan PM atau CM yang mengubah sistem dicatat di Service Report beserta nomor tiket Zammad atau CR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="33">
-      <c r="A21" s="39" t="inlineStr">
+          <t>Catat setiap pelaksanaan PM atau CM yang mengubah sistem di Service Report, beserta nomor ticket Zammad atau CR.</t>
+        </is>
+      </c>
+      <c r="C20" s="62" t="n"/>
+      <c r="D20" s="62" t="n"/>
+      <c r="E20" s="62" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="33">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>Lead NOC meninjau kepatuhan bulanan dan menandatangani kolom verifikasi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="33">
-      <c r="A23" s="38" t="inlineStr">
+          <t>Setiap bulan, Lead NOC meninjau kepatuhan dan menandatangani kolom verifikasi.</t>
+        </is>
+      </c>
+      <c r="C21" s="62" t="n"/>
+      <c r="D21" s="62" t="n"/>
+      <c r="E21" s="62" t="n"/>
+    </row>
+    <row r="22" s="33">
+      <c r="A22" s="62" t="n"/>
+      <c r="B22" s="62" t="n"/>
+      <c r="C22" s="62" t="n"/>
+      <c r="D22" s="62" t="n"/>
+      <c r="E22" s="62" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="33">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="33">
-      <c r="A24" s="41" t="n"/>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B23" s="62" t="n"/>
+      <c r="C23" s="62" t="n"/>
+      <c r="D23" s="62" t="n"/>
+      <c r="E23" s="62" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="33">
+      <c r="A24" s="65" t="n"/>
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="33">
-      <c r="A25" s="42" t="n"/>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="C24" s="62" t="n"/>
+      <c r="D24" s="62" t="n"/>
+      <c r="E24" s="62" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="33">
+      <c r="A25" s="66" t="n"/>
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Biru muda: warna baris contoh, sudah dikosongkan dan tidak dipakai</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="33">
-      <c r="A26" s="43" t="n"/>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="C25" s="62" t="n"/>
+      <c r="D25" s="62" t="n"/>
+      <c r="E25" s="62" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="33">
+      <c r="A26" s="67" t="n"/>
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="33">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="C26" s="62" t="n"/>
+      <c r="D26" s="62" t="n"/>
+      <c r="E26" s="62" t="n"/>
+    </row>
+    <row r="27" s="33">
+      <c r="A27" s="62" t="n"/>
+      <c r="B27" s="62" t="n"/>
+      <c r="C27" s="62" t="n"/>
+      <c r="D27" s="62" t="n"/>
+      <c r="E27" s="62" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="33">
+      <c r="A28" s="64" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="33">
-      <c r="A29" s="44" t="inlineStr">
+      <c r="B28" s="62" t="n"/>
+      <c r="C28" s="62" t="n"/>
+      <c r="D28" s="62" t="n"/>
+      <c r="E28" s="62" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="33">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="57" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C29" s="44" t="inlineStr">
+      <c r="C29" s="57" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D29" s="44" t="inlineStr">
+      <c r="D29" s="57" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E29" s="44" t="inlineStr">
+      <c r="E29" s="57" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="33">
+    <row r="30" ht="30" customHeight="1" s="33">
       <c r="A30" s="37" t="inlineStr">
         <is>
           <t>00</t>
@@ -1066,76 +1208,91 @@
       <c r="D31" s="37" t="n"/>
       <c r="E31" s="37" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="33">
-      <c r="A33" s="38" t="inlineStr">
+    <row r="32" s="33">
+      <c r="A32" s="62" t="n"/>
+      <c r="B32" s="62" t="n"/>
+      <c r="C32" s="62" t="n"/>
+      <c r="D32" s="62" t="n"/>
+      <c r="E32" s="62" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="33">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="33">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="B33" s="62" t="n"/>
+      <c r="C33" s="62" t="n"/>
+      <c r="D33" s="62" t="n"/>
+      <c r="E33" s="62" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="33">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="57" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C34" s="44" t="inlineStr">
+      <c r="C34" s="57" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
+      <c r="D34" s="57" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E34" s="62" t="n"/>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="33">
-      <c r="A35" s="45" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C35" s="45" t="n"/>
-      <c r="D35" s="45" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="62" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="33">
-      <c r="A36" s="45" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B36" s="45" t="inlineStr">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C36" s="45" t="n"/>
-      <c r="D36" s="45" t="n"/>
+      <c r="C36" s="37" t="n"/>
+      <c r="D36" s="37" t="n"/>
+      <c r="E36" s="62" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="33">
-      <c r="A37" s="45" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B37" s="45" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="37" t="n"/>
+      <c r="E37" s="62" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1179,72 +1336,75 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="32" min="1" max="3"/>
+    <col width="13" customWidth="1" style="33" min="2" max="2"/>
+    <col width="13" customWidth="1" style="33" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="33">
-      <c r="A1" s="47" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="33">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>Kode bulan</t>
         </is>
       </c>
-      <c r="B1" s="47" t="inlineStr">
+      <c r="B1" s="68" t="inlineStr">
         <is>
           <t>Jenis</t>
         </is>
       </c>
-      <c r="C1" s="47" t="inlineStr">
+      <c r="C1" s="68" t="inlineStr">
         <is>
           <t>Status SR</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="33">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B2" s="39" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="33">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="69" t="inlineStr">
         <is>
           <t>Selesai</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="33">
-      <c r="A3" s="39" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="33">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>Tindak lanjut</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="33">
-      <c r="A4" s="39" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="33">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="B4" s="70" t="n"/>
+      <c r="C4" s="69" t="inlineStr">
         <is>
           <t>Eskalasi</t>
         </is>
@@ -1253,7 +1413,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1261,7 +1421,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1272,7 +1432,20 @@
     <col width="14" customWidth="1" style="32" min="4" max="4"/>
     <col width="15" customWidth="1" style="32" min="5" max="5"/>
     <col width="5" customWidth="1" style="32" min="6" max="17"/>
-    <col width="10" customWidth="1" style="32" min="18" max="20"/>
+    <col width="13" customWidth="1" style="33" min="7" max="7"/>
+    <col width="13" customWidth="1" style="33" min="8" max="8"/>
+    <col width="13" customWidth="1" style="33" min="9" max="9"/>
+    <col width="13" customWidth="1" style="33" min="10" max="10"/>
+    <col width="13" customWidth="1" style="33" min="11" max="11"/>
+    <col width="13" customWidth="1" style="33" min="12" max="12"/>
+    <col width="13" customWidth="1" style="33" min="13" max="13"/>
+    <col width="13" customWidth="1" style="33" min="14" max="14"/>
+    <col width="13" customWidth="1" style="33" min="15" max="15"/>
+    <col width="13" customWidth="1" style="33" min="16" max="16"/>
+    <col width="13" customWidth="1" style="33" min="17" max="17"/>
+    <col width="11" customWidth="1" style="32" min="18" max="20"/>
+    <col width="13" customWidth="1" style="33" min="19" max="19"/>
+    <col width="14" customWidth="1" style="33" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="33">
@@ -1299,7 +1472,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="33">
+    <row r="5" ht="16.5" customHeight="1" s="33">
       <c r="A5" s="50" t="inlineStr">
         <is>
           <t>No</t>
@@ -1401,8 +1574,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="33">
-      <c r="A6" s="51" t="n">
+    <row r="6" ht="27.3" customHeight="1" s="33">
+      <c r="A6" s="71" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="52" t="inlineStr">
@@ -1485,21 +1658,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="72">
         <f>COUNTIF(F6:Q6,"R")+COUNTIF(F6:Q6,"S")+COUNTIF(F6:Q6,"T")</f>
         <v/>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="72">
         <f>COUNTIF(F6:Q6,"S")</f>
         <v/>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="73">
         <f>IF(R6=0,"",S6/R6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="33">
-      <c r="A7" s="51" t="n">
+    <row r="7" ht="27.3" customHeight="1" s="33">
+      <c r="A7" s="71" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="52" t="inlineStr">
@@ -1582,21 +1755,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R7" s="43">
+      <c r="R7" s="72">
         <f>COUNTIF(F7:Q7,"R")+COUNTIF(F7:Q7,"S")+COUNTIF(F7:Q7,"T")</f>
         <v/>
       </c>
-      <c r="S7" s="43">
+      <c r="S7" s="72">
         <f>COUNTIF(F7:Q7,"S")</f>
         <v/>
       </c>
-      <c r="T7" s="54">
+      <c r="T7" s="73">
         <f>IF(R7=0,"",S7/R7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="33">
-      <c r="A8" s="51" t="n">
+    <row r="8" ht="27.3" customHeight="1" s="33">
+      <c r="A8" s="71" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="52" t="inlineStr">
@@ -1679,21 +1852,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R8" s="43">
+      <c r="R8" s="72">
         <f>COUNTIF(F8:Q8,"R")+COUNTIF(F8:Q8,"S")+COUNTIF(F8:Q8,"T")</f>
         <v/>
       </c>
-      <c r="S8" s="43">
+      <c r="S8" s="72">
         <f>COUNTIF(F8:Q8,"S")</f>
         <v/>
       </c>
-      <c r="T8" s="54">
+      <c r="T8" s="73">
         <f>IF(R8=0,"",S8/R8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="33">
-      <c r="A9" s="51" t="n">
+    <row r="9" ht="27.3" customHeight="1" s="33">
+      <c r="A9" s="71" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="52" t="inlineStr">
@@ -1776,21 +1949,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R9" s="43">
+      <c r="R9" s="72">
         <f>COUNTIF(F9:Q9,"R")+COUNTIF(F9:Q9,"S")+COUNTIF(F9:Q9,"T")</f>
         <v/>
       </c>
-      <c r="S9" s="43">
+      <c r="S9" s="72">
         <f>COUNTIF(F9:Q9,"S")</f>
         <v/>
       </c>
-      <c r="T9" s="54">
+      <c r="T9" s="73">
         <f>IF(R9=0,"",S9/R9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="33">
-      <c r="A10" s="51" t="n">
+    <row r="10" ht="27.3" customHeight="1" s="33">
+      <c r="A10" s="71" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="52" t="inlineStr">
@@ -1873,21 +2046,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R10" s="43">
+      <c r="R10" s="72">
         <f>COUNTIF(F10:Q10,"R")+COUNTIF(F10:Q10,"S")+COUNTIF(F10:Q10,"T")</f>
         <v/>
       </c>
-      <c r="S10" s="43">
+      <c r="S10" s="72">
         <f>COUNTIF(F10:Q10,"S")</f>
         <v/>
       </c>
-      <c r="T10" s="54">
+      <c r="T10" s="73">
         <f>IF(R10=0,"",S10/R10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="22.35" customHeight="1" s="33">
-      <c r="A11" s="51" t="n">
+    <row r="11" ht="27.3" customHeight="1" s="33">
+      <c r="A11" s="71" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="52" t="inlineStr">
@@ -1970,21 +2143,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R11" s="43">
+      <c r="R11" s="72">
         <f>COUNTIF(F11:Q11,"R")+COUNTIF(F11:Q11,"S")+COUNTIF(F11:Q11,"T")</f>
         <v/>
       </c>
-      <c r="S11" s="43">
+      <c r="S11" s="72">
         <f>COUNTIF(F11:Q11,"S")</f>
         <v/>
       </c>
-      <c r="T11" s="54">
+      <c r="T11" s="73">
         <f>IF(R11=0,"",S11/R11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="33">
-      <c r="A12" s="51" t="n">
+    <row r="12" ht="27.3" customHeight="1" s="33">
+      <c r="A12" s="71" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="52" t="inlineStr">
@@ -2067,21 +2240,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R12" s="43">
+      <c r="R12" s="72">
         <f>COUNTIF(F12:Q12,"R")+COUNTIF(F12:Q12,"S")+COUNTIF(F12:Q12,"T")</f>
         <v/>
       </c>
-      <c r="S12" s="43">
+      <c r="S12" s="72">
         <f>COUNTIF(F12:Q12,"S")</f>
         <v/>
       </c>
-      <c r="T12" s="54">
+      <c r="T12" s="73">
         <f>IF(R12=0,"",S12/R12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="33">
-      <c r="A13" s="51" t="n">
+    <row r="13" ht="27.3" customHeight="1" s="33">
+      <c r="A13" s="71" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="52" t="inlineStr">
@@ -2132,21 +2305,21 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R13" s="43">
+      <c r="R13" s="72">
         <f>COUNTIF(F13:Q13,"R")+COUNTIF(F13:Q13,"S")+COUNTIF(F13:Q13,"T")</f>
         <v/>
       </c>
-      <c r="S13" s="43">
+      <c r="S13" s="72">
         <f>COUNTIF(F13:Q13,"S")</f>
         <v/>
       </c>
-      <c r="T13" s="54">
+      <c r="T13" s="73">
         <f>IF(R13=0,"",S13/R13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="33">
-      <c r="A14" s="51" t="n">
+    <row r="14" ht="27.3" customHeight="1" s="33">
+      <c r="A14" s="71" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="52" t="inlineStr">
@@ -2185,21 +2358,21 @@
         </is>
       </c>
       <c r="Q14" s="53" t="n"/>
-      <c r="R14" s="43">
+      <c r="R14" s="72">
         <f>COUNTIF(F14:Q14,"R")+COUNTIF(F14:Q14,"S")+COUNTIF(F14:Q14,"T")</f>
         <v/>
       </c>
-      <c r="S14" s="43">
+      <c r="S14" s="72">
         <f>COUNTIF(F14:Q14,"S")</f>
         <v/>
       </c>
-      <c r="T14" s="54">
+      <c r="T14" s="73">
         <f>IF(R14=0,"",S14/R14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="33">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="71" t="n"/>
       <c r="B15" s="52" t="n"/>
       <c r="C15" s="52" t="n"/>
       <c r="D15" s="52" t="n"/>
@@ -2216,21 +2389,21 @@
       <c r="O15" s="53" t="n"/>
       <c r="P15" s="53" t="n"/>
       <c r="Q15" s="53" t="n"/>
-      <c r="R15" s="43">
+      <c r="R15" s="72">
         <f>COUNTIF(F15:Q15,"R")+COUNTIF(F15:Q15,"S")+COUNTIF(F15:Q15,"T")</f>
         <v/>
       </c>
-      <c r="S15" s="43">
+      <c r="S15" s="72">
         <f>COUNTIF(F15:Q15,"S")</f>
         <v/>
       </c>
-      <c r="T15" s="54">
+      <c r="T15" s="73">
         <f>IF(R15=0,"",S15/R15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="33">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="71" t="n"/>
       <c r="B16" s="52" t="n"/>
       <c r="C16" s="52" t="n"/>
       <c r="D16" s="52" t="n"/>
@@ -2247,21 +2420,21 @@
       <c r="O16" s="53" t="n"/>
       <c r="P16" s="53" t="n"/>
       <c r="Q16" s="53" t="n"/>
-      <c r="R16" s="43">
+      <c r="R16" s="72">
         <f>COUNTIF(F16:Q16,"R")+COUNTIF(F16:Q16,"S")+COUNTIF(F16:Q16,"T")</f>
         <v/>
       </c>
-      <c r="S16" s="43">
+      <c r="S16" s="72">
         <f>COUNTIF(F16:Q16,"S")</f>
         <v/>
       </c>
-      <c r="T16" s="54">
+      <c r="T16" s="73">
         <f>IF(R16=0,"",S16/R16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="33">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="71" t="n"/>
       <c r="B17" s="52" t="n"/>
       <c r="C17" s="52" t="n"/>
       <c r="D17" s="52" t="n"/>
@@ -2278,21 +2451,21 @@
       <c r="O17" s="53" t="n"/>
       <c r="P17" s="53" t="n"/>
       <c r="Q17" s="53" t="n"/>
-      <c r="R17" s="43">
+      <c r="R17" s="72">
         <f>COUNTIF(F17:Q17,"R")+COUNTIF(F17:Q17,"S")+COUNTIF(F17:Q17,"T")</f>
         <v/>
       </c>
-      <c r="S17" s="43">
+      <c r="S17" s="72">
         <f>COUNTIF(F17:Q17,"S")</f>
         <v/>
       </c>
-      <c r="T17" s="54">
+      <c r="T17" s="73">
         <f>IF(R17=0,"",S17/R17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="33">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="71" t="n"/>
       <c r="B18" s="52" t="n"/>
       <c r="C18" s="52" t="n"/>
       <c r="D18" s="52" t="n"/>
@@ -2309,21 +2482,21 @@
       <c r="O18" s="53" t="n"/>
       <c r="P18" s="53" t="n"/>
       <c r="Q18" s="53" t="n"/>
-      <c r="R18" s="43">
+      <c r="R18" s="72">
         <f>COUNTIF(F18:Q18,"R")+COUNTIF(F18:Q18,"S")+COUNTIF(F18:Q18,"T")</f>
         <v/>
       </c>
-      <c r="S18" s="43">
+      <c r="S18" s="72">
         <f>COUNTIF(F18:Q18,"S")</f>
         <v/>
       </c>
-      <c r="T18" s="54">
+      <c r="T18" s="73">
         <f>IF(R18=0,"",S18/R18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="33">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="71" t="n"/>
       <c r="B19" s="52" t="n"/>
       <c r="C19" s="52" t="n"/>
       <c r="D19" s="52" t="n"/>
@@ -2340,21 +2513,21 @@
       <c r="O19" s="53" t="n"/>
       <c r="P19" s="53" t="n"/>
       <c r="Q19" s="53" t="n"/>
-      <c r="R19" s="43">
+      <c r="R19" s="72">
         <f>COUNTIF(F19:Q19,"R")+COUNTIF(F19:Q19,"S")+COUNTIF(F19:Q19,"T")</f>
         <v/>
       </c>
-      <c r="S19" s="43">
+      <c r="S19" s="72">
         <f>COUNTIF(F19:Q19,"S")</f>
         <v/>
       </c>
-      <c r="T19" s="54">
+      <c r="T19" s="73">
         <f>IF(R19=0,"",S19/R19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="33">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="71" t="n"/>
       <c r="B20" s="52" t="n"/>
       <c r="C20" s="52" t="n"/>
       <c r="D20" s="52" t="n"/>
@@ -2371,21 +2544,21 @@
       <c r="O20" s="53" t="n"/>
       <c r="P20" s="53" t="n"/>
       <c r="Q20" s="53" t="n"/>
-      <c r="R20" s="43">
+      <c r="R20" s="72">
         <f>COUNTIF(F20:Q20,"R")+COUNTIF(F20:Q20,"S")+COUNTIF(F20:Q20,"T")</f>
         <v/>
       </c>
-      <c r="S20" s="43">
+      <c r="S20" s="72">
         <f>COUNTIF(F20:Q20,"S")</f>
         <v/>
       </c>
-      <c r="T20" s="54">
+      <c r="T20" s="73">
         <f>IF(R20=0,"",S20/R20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="33">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="71" t="n"/>
       <c r="B21" s="52" t="n"/>
       <c r="C21" s="52" t="n"/>
       <c r="D21" s="52" t="n"/>
@@ -2402,21 +2575,21 @@
       <c r="O21" s="53" t="n"/>
       <c r="P21" s="53" t="n"/>
       <c r="Q21" s="53" t="n"/>
-      <c r="R21" s="43">
+      <c r="R21" s="72">
         <f>COUNTIF(F21:Q21,"R")+COUNTIF(F21:Q21,"S")+COUNTIF(F21:Q21,"T")</f>
         <v/>
       </c>
-      <c r="S21" s="43">
+      <c r="S21" s="72">
         <f>COUNTIF(F21:Q21,"S")</f>
         <v/>
       </c>
-      <c r="T21" s="54">
+      <c r="T21" s="73">
         <f>IF(R21=0,"",S21/R21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="33">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="71" t="n"/>
       <c r="B22" s="52" t="n"/>
       <c r="C22" s="52" t="n"/>
       <c r="D22" s="52" t="n"/>
@@ -2433,21 +2606,21 @@
       <c r="O22" s="53" t="n"/>
       <c r="P22" s="53" t="n"/>
       <c r="Q22" s="53" t="n"/>
-      <c r="R22" s="43">
+      <c r="R22" s="72">
         <f>COUNTIF(F22:Q22,"R")+COUNTIF(F22:Q22,"S")+COUNTIF(F22:Q22,"T")</f>
         <v/>
       </c>
-      <c r="S22" s="43">
+      <c r="S22" s="72">
         <f>COUNTIF(F22:Q22,"S")</f>
         <v/>
       </c>
-      <c r="T22" s="54">
+      <c r="T22" s="73">
         <f>IF(R22=0,"",S22/R22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="33">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="71" t="n"/>
       <c r="B23" s="52" t="n"/>
       <c r="C23" s="52" t="n"/>
       <c r="D23" s="52" t="n"/>
@@ -2464,21 +2637,21 @@
       <c r="O23" s="53" t="n"/>
       <c r="P23" s="53" t="n"/>
       <c r="Q23" s="53" t="n"/>
-      <c r="R23" s="43">
+      <c r="R23" s="72">
         <f>COUNTIF(F23:Q23,"R")+COUNTIF(F23:Q23,"S")+COUNTIF(F23:Q23,"T")</f>
         <v/>
       </c>
-      <c r="S23" s="43">
+      <c r="S23" s="72">
         <f>COUNTIF(F23:Q23,"S")</f>
         <v/>
       </c>
-      <c r="T23" s="54">
+      <c r="T23" s="73">
         <f>IF(R23=0,"",S23/R23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="33">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="71" t="n"/>
       <c r="B24" s="52" t="n"/>
       <c r="C24" s="52" t="n"/>
       <c r="D24" s="52" t="n"/>
@@ -2495,21 +2668,21 @@
       <c r="O24" s="53" t="n"/>
       <c r="P24" s="53" t="n"/>
       <c r="Q24" s="53" t="n"/>
-      <c r="R24" s="43">
+      <c r="R24" s="72">
         <f>COUNTIF(F24:Q24,"R")+COUNTIF(F24:Q24,"S")+COUNTIF(F24:Q24,"T")</f>
         <v/>
       </c>
-      <c r="S24" s="43">
+      <c r="S24" s="72">
         <f>COUNTIF(F24:Q24,"S")</f>
         <v/>
       </c>
-      <c r="T24" s="54">
+      <c r="T24" s="73">
         <f>IF(R24=0,"",S24/R24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="33">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="71" t="n"/>
       <c r="B25" s="52" t="n"/>
       <c r="C25" s="52" t="n"/>
       <c r="D25" s="52" t="n"/>
@@ -2526,21 +2699,21 @@
       <c r="O25" s="53" t="n"/>
       <c r="P25" s="53" t="n"/>
       <c r="Q25" s="53" t="n"/>
-      <c r="R25" s="43">
+      <c r="R25" s="72">
         <f>COUNTIF(F25:Q25,"R")+COUNTIF(F25:Q25,"S")+COUNTIF(F25:Q25,"T")</f>
         <v/>
       </c>
-      <c r="S25" s="43">
+      <c r="S25" s="72">
         <f>COUNTIF(F25:Q25,"S")</f>
         <v/>
       </c>
-      <c r="T25" s="54">
+      <c r="T25" s="73">
         <f>IF(R25=0,"",S25/R25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="33">
-      <c r="A26" s="51" t="n"/>
+      <c r="A26" s="71" t="n"/>
       <c r="B26" s="52" t="n"/>
       <c r="C26" s="52" t="n"/>
       <c r="D26" s="52" t="n"/>
@@ -2557,21 +2730,21 @@
       <c r="O26" s="53" t="n"/>
       <c r="P26" s="53" t="n"/>
       <c r="Q26" s="53" t="n"/>
-      <c r="R26" s="43">
+      <c r="R26" s="72">
         <f>COUNTIF(F26:Q26,"R")+COUNTIF(F26:Q26,"S")+COUNTIF(F26:Q26,"T")</f>
         <v/>
       </c>
-      <c r="S26" s="43">
+      <c r="S26" s="72">
         <f>COUNTIF(F26:Q26,"S")</f>
         <v/>
       </c>
-      <c r="T26" s="54">
+      <c r="T26" s="73">
         <f>IF(R26=0,"",S26/R26)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="33">
-      <c r="A27" s="51" t="n"/>
+      <c r="A27" s="71" t="n"/>
       <c r="B27" s="52" t="n"/>
       <c r="C27" s="52" t="n"/>
       <c r="D27" s="52" t="n"/>
@@ -2588,21 +2761,21 @@
       <c r="O27" s="53" t="n"/>
       <c r="P27" s="53" t="n"/>
       <c r="Q27" s="53" t="n"/>
-      <c r="R27" s="43">
+      <c r="R27" s="72">
         <f>COUNTIF(F27:Q27,"R")+COUNTIF(F27:Q27,"S")+COUNTIF(F27:Q27,"T")</f>
         <v/>
       </c>
-      <c r="S27" s="43">
+      <c r="S27" s="72">
         <f>COUNTIF(F27:Q27,"S")</f>
         <v/>
       </c>
-      <c r="T27" s="54">
+      <c r="T27" s="73">
         <f>IF(R27=0,"",S27/R27)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="33">
-      <c r="A28" s="51" t="n"/>
+      <c r="A28" s="71" t="n"/>
       <c r="B28" s="52" t="n"/>
       <c r="C28" s="52" t="n"/>
       <c r="D28" s="52" t="n"/>
@@ -2619,21 +2792,21 @@
       <c r="O28" s="53" t="n"/>
       <c r="P28" s="53" t="n"/>
       <c r="Q28" s="53" t="n"/>
-      <c r="R28" s="43">
+      <c r="R28" s="72">
         <f>COUNTIF(F28:Q28,"R")+COUNTIF(F28:Q28,"S")+COUNTIF(F28:Q28,"T")</f>
         <v/>
       </c>
-      <c r="S28" s="43">
+      <c r="S28" s="72">
         <f>COUNTIF(F28:Q28,"S")</f>
         <v/>
       </c>
-      <c r="T28" s="54">
+      <c r="T28" s="73">
         <f>IF(R28=0,"",S28/R28)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="33">
-      <c r="A29" s="51" t="n"/>
+      <c r="A29" s="71" t="n"/>
       <c r="B29" s="52" t="n"/>
       <c r="C29" s="52" t="n"/>
       <c r="D29" s="52" t="n"/>
@@ -2650,21 +2823,21 @@
       <c r="O29" s="53" t="n"/>
       <c r="P29" s="53" t="n"/>
       <c r="Q29" s="53" t="n"/>
-      <c r="R29" s="43">
+      <c r="R29" s="72">
         <f>COUNTIF(F29:Q29,"R")+COUNTIF(F29:Q29,"S")+COUNTIF(F29:Q29,"T")</f>
         <v/>
       </c>
-      <c r="S29" s="43">
+      <c r="S29" s="72">
         <f>COUNTIF(F29:Q29,"S")</f>
         <v/>
       </c>
-      <c r="T29" s="54">
+      <c r="T29" s="73">
         <f>IF(R29=0,"",S29/R29)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="33">
-      <c r="A30" s="51" t="n"/>
+      <c r="A30" s="71" t="n"/>
       <c r="B30" s="52" t="n"/>
       <c r="C30" s="52" t="n"/>
       <c r="D30" s="52" t="n"/>
@@ -2681,21 +2854,21 @@
       <c r="O30" s="53" t="n"/>
       <c r="P30" s="53" t="n"/>
       <c r="Q30" s="53" t="n"/>
-      <c r="R30" s="43">
+      <c r="R30" s="72">
         <f>COUNTIF(F30:Q30,"R")+COUNTIF(F30:Q30,"S")+COUNTIF(F30:Q30,"T")</f>
         <v/>
       </c>
-      <c r="S30" s="43">
+      <c r="S30" s="72">
         <f>COUNTIF(F30:Q30,"S")</f>
         <v/>
       </c>
-      <c r="T30" s="54">
+      <c r="T30" s="73">
         <f>IF(R30=0,"",S30/R30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="33">
-      <c r="A31" s="51" t="n"/>
+      <c r="A31" s="71" t="n"/>
       <c r="B31" s="52" t="n"/>
       <c r="C31" s="52" t="n"/>
       <c r="D31" s="52" t="n"/>
@@ -2712,21 +2885,21 @@
       <c r="O31" s="53" t="n"/>
       <c r="P31" s="53" t="n"/>
       <c r="Q31" s="53" t="n"/>
-      <c r="R31" s="43">
+      <c r="R31" s="72">
         <f>COUNTIF(F31:Q31,"R")+COUNTIF(F31:Q31,"S")+COUNTIF(F31:Q31,"T")</f>
         <v/>
       </c>
-      <c r="S31" s="43">
+      <c r="S31" s="72">
         <f>COUNTIF(F31:Q31,"S")</f>
         <v/>
       </c>
-      <c r="T31" s="54">
+      <c r="T31" s="73">
         <f>IF(R31=0,"",S31/R31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="33">
-      <c r="A32" s="51" t="n"/>
+      <c r="A32" s="71" t="n"/>
       <c r="B32" s="52" t="n"/>
       <c r="C32" s="52" t="n"/>
       <c r="D32" s="52" t="n"/>
@@ -2743,21 +2916,21 @@
       <c r="O32" s="53" t="n"/>
       <c r="P32" s="53" t="n"/>
       <c r="Q32" s="53" t="n"/>
-      <c r="R32" s="43">
+      <c r="R32" s="72">
         <f>COUNTIF(F32:Q32,"R")+COUNTIF(F32:Q32,"S")+COUNTIF(F32:Q32,"T")</f>
         <v/>
       </c>
-      <c r="S32" s="43">
+      <c r="S32" s="72">
         <f>COUNTIF(F32:Q32,"S")</f>
         <v/>
       </c>
-      <c r="T32" s="54">
+      <c r="T32" s="73">
         <f>IF(R32=0,"",S32/R32)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="33">
-      <c r="A33" s="51" t="n"/>
+      <c r="A33" s="71" t="n"/>
       <c r="B33" s="52" t="n"/>
       <c r="C33" s="52" t="n"/>
       <c r="D33" s="52" t="n"/>
@@ -2774,21 +2947,21 @@
       <c r="O33" s="53" t="n"/>
       <c r="P33" s="53" t="n"/>
       <c r="Q33" s="53" t="n"/>
-      <c r="R33" s="43">
+      <c r="R33" s="72">
         <f>COUNTIF(F33:Q33,"R")+COUNTIF(F33:Q33,"S")+COUNTIF(F33:Q33,"T")</f>
         <v/>
       </c>
-      <c r="S33" s="43">
+      <c r="S33" s="72">
         <f>COUNTIF(F33:Q33,"S")</f>
         <v/>
       </c>
-      <c r="T33" s="54">
+      <c r="T33" s="73">
         <f>IF(R33=0,"",S33/R33)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="33">
-      <c r="A34" s="51" t="n"/>
+      <c r="A34" s="71" t="n"/>
       <c r="B34" s="52" t="n"/>
       <c r="C34" s="52" t="n"/>
       <c r="D34" s="52" t="n"/>
@@ -2805,21 +2978,21 @@
       <c r="O34" s="53" t="n"/>
       <c r="P34" s="53" t="n"/>
       <c r="Q34" s="53" t="n"/>
-      <c r="R34" s="43">
+      <c r="R34" s="72">
         <f>COUNTIF(F34:Q34,"R")+COUNTIF(F34:Q34,"S")+COUNTIF(F34:Q34,"T")</f>
         <v/>
       </c>
-      <c r="S34" s="43">
+      <c r="S34" s="72">
         <f>COUNTIF(F34:Q34,"S")</f>
         <v/>
       </c>
-      <c r="T34" s="54">
+      <c r="T34" s="73">
         <f>IF(R34=0,"",S34/R34)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="33">
-      <c r="A35" s="51" t="n"/>
+      <c r="A35" s="71" t="n"/>
       <c r="B35" s="52" t="n"/>
       <c r="C35" s="52" t="n"/>
       <c r="D35" s="52" t="n"/>
@@ -2836,21 +3009,21 @@
       <c r="O35" s="53" t="n"/>
       <c r="P35" s="53" t="n"/>
       <c r="Q35" s="53" t="n"/>
-      <c r="R35" s="43">
+      <c r="R35" s="72">
         <f>COUNTIF(F35:Q35,"R")+COUNTIF(F35:Q35,"S")+COUNTIF(F35:Q35,"T")</f>
         <v/>
       </c>
-      <c r="S35" s="43">
+      <c r="S35" s="72">
         <f>COUNTIF(F35:Q35,"S")</f>
         <v/>
       </c>
-      <c r="T35" s="54">
+      <c r="T35" s="73">
         <f>IF(R35=0,"",S35/R35)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="33">
-      <c r="A36" s="51" t="n"/>
+      <c r="A36" s="71" t="n"/>
       <c r="B36" s="52" t="n"/>
       <c r="C36" s="52" t="n"/>
       <c r="D36" s="52" t="n"/>
@@ -2867,21 +3040,21 @@
       <c r="O36" s="53" t="n"/>
       <c r="P36" s="53" t="n"/>
       <c r="Q36" s="53" t="n"/>
-      <c r="R36" s="43">
+      <c r="R36" s="72">
         <f>COUNTIF(F36:Q36,"R")+COUNTIF(F36:Q36,"S")+COUNTIF(F36:Q36,"T")</f>
         <v/>
       </c>
-      <c r="S36" s="43">
+      <c r="S36" s="72">
         <f>COUNTIF(F36:Q36,"S")</f>
         <v/>
       </c>
-      <c r="T36" s="54">
+      <c r="T36" s="73">
         <f>IF(R36=0,"",S36/R36)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="33">
-      <c r="A37" s="51" t="n"/>
+      <c r="A37" s="71" t="n"/>
       <c r="B37" s="52" t="n"/>
       <c r="C37" s="52" t="n"/>
       <c r="D37" s="52" t="n"/>
@@ -2898,21 +3071,21 @@
       <c r="O37" s="53" t="n"/>
       <c r="P37" s="53" t="n"/>
       <c r="Q37" s="53" t="n"/>
-      <c r="R37" s="43">
+      <c r="R37" s="72">
         <f>COUNTIF(F37:Q37,"R")+COUNTIF(F37:Q37,"S")+COUNTIF(F37:Q37,"T")</f>
         <v/>
       </c>
-      <c r="S37" s="43">
+      <c r="S37" s="72">
         <f>COUNTIF(F37:Q37,"S")</f>
         <v/>
       </c>
-      <c r="T37" s="54">
+      <c r="T37" s="73">
         <f>IF(R37=0,"",S37/R37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="33">
-      <c r="A38" s="51" t="n"/>
+      <c r="A38" s="71" t="n"/>
       <c r="B38" s="52" t="n"/>
       <c r="C38" s="52" t="n"/>
       <c r="D38" s="52" t="n"/>
@@ -2929,21 +3102,21 @@
       <c r="O38" s="53" t="n"/>
       <c r="P38" s="53" t="n"/>
       <c r="Q38" s="53" t="n"/>
-      <c r="R38" s="43">
+      <c r="R38" s="72">
         <f>COUNTIF(F38:Q38,"R")+COUNTIF(F38:Q38,"S")+COUNTIF(F38:Q38,"T")</f>
         <v/>
       </c>
-      <c r="S38" s="43">
+      <c r="S38" s="72">
         <f>COUNTIF(F38:Q38,"S")</f>
         <v/>
       </c>
-      <c r="T38" s="54">
+      <c r="T38" s="73">
         <f>IF(R38=0,"",S38/R38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="33">
-      <c r="A39" s="51" t="n"/>
+      <c r="A39" s="71" t="n"/>
       <c r="B39" s="52" t="n"/>
       <c r="C39" s="52" t="n"/>
       <c r="D39" s="52" t="n"/>
@@ -2960,21 +3133,21 @@
       <c r="O39" s="53" t="n"/>
       <c r="P39" s="53" t="n"/>
       <c r="Q39" s="53" t="n"/>
-      <c r="R39" s="43">
+      <c r="R39" s="72">
         <f>COUNTIF(F39:Q39,"R")+COUNTIF(F39:Q39,"S")+COUNTIF(F39:Q39,"T")</f>
         <v/>
       </c>
-      <c r="S39" s="43">
+      <c r="S39" s="72">
         <f>COUNTIF(F39:Q39,"S")</f>
         <v/>
       </c>
-      <c r="T39" s="54">
+      <c r="T39" s="73">
         <f>IF(R39=0,"",S39/R39)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="33">
-      <c r="A40" s="51" t="n"/>
+      <c r="A40" s="71" t="n"/>
       <c r="B40" s="52" t="n"/>
       <c r="C40" s="52" t="n"/>
       <c r="D40" s="52" t="n"/>
@@ -2991,21 +3164,21 @@
       <c r="O40" s="53" t="n"/>
       <c r="P40" s="53" t="n"/>
       <c r="Q40" s="53" t="n"/>
-      <c r="R40" s="43">
+      <c r="R40" s="72">
         <f>COUNTIF(F40:Q40,"R")+COUNTIF(F40:Q40,"S")+COUNTIF(F40:Q40,"T")</f>
         <v/>
       </c>
-      <c r="S40" s="43">
+      <c r="S40" s="72">
         <f>COUNTIF(F40:Q40,"S")</f>
         <v/>
       </c>
-      <c r="T40" s="54">
+      <c r="T40" s="73">
         <f>IF(R40=0,"",S40/R40)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="33">
-      <c r="A41" s="51" t="n"/>
+      <c r="A41" s="71" t="n"/>
       <c r="B41" s="52" t="n"/>
       <c r="C41" s="52" t="n"/>
       <c r="D41" s="52" t="n"/>
@@ -3022,21 +3195,21 @@
       <c r="O41" s="53" t="n"/>
       <c r="P41" s="53" t="n"/>
       <c r="Q41" s="53" t="n"/>
-      <c r="R41" s="43">
+      <c r="R41" s="72">
         <f>COUNTIF(F41:Q41,"R")+COUNTIF(F41:Q41,"S")+COUNTIF(F41:Q41,"T")</f>
         <v/>
       </c>
-      <c r="S41" s="43">
+      <c r="S41" s="72">
         <f>COUNTIF(F41:Q41,"S")</f>
         <v/>
       </c>
-      <c r="T41" s="54">
+      <c r="T41" s="73">
         <f>IF(R41=0,"",S41/R41)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="33">
-      <c r="A42" s="51" t="n"/>
+      <c r="A42" s="71" t="n"/>
       <c r="B42" s="52" t="n"/>
       <c r="C42" s="52" t="n"/>
       <c r="D42" s="52" t="n"/>
@@ -3053,21 +3226,21 @@
       <c r="O42" s="53" t="n"/>
       <c r="P42" s="53" t="n"/>
       <c r="Q42" s="53" t="n"/>
-      <c r="R42" s="43">
+      <c r="R42" s="72">
         <f>COUNTIF(F42:Q42,"R")+COUNTIF(F42:Q42,"S")+COUNTIF(F42:Q42,"T")</f>
         <v/>
       </c>
-      <c r="S42" s="43">
+      <c r="S42" s="72">
         <f>COUNTIF(F42:Q42,"S")</f>
         <v/>
       </c>
-      <c r="T42" s="54">
+      <c r="T42" s="73">
         <f>IF(R42=0,"",S42/R42)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="33">
-      <c r="A43" s="51" t="n"/>
+      <c r="A43" s="71" t="n"/>
       <c r="B43" s="52" t="n"/>
       <c r="C43" s="52" t="n"/>
       <c r="D43" s="52" t="n"/>
@@ -3084,21 +3257,21 @@
       <c r="O43" s="53" t="n"/>
       <c r="P43" s="53" t="n"/>
       <c r="Q43" s="53" t="n"/>
-      <c r="R43" s="43">
+      <c r="R43" s="72">
         <f>COUNTIF(F43:Q43,"R")+COUNTIF(F43:Q43,"S")+COUNTIF(F43:Q43,"T")</f>
         <v/>
       </c>
-      <c r="S43" s="43">
+      <c r="S43" s="72">
         <f>COUNTIF(F43:Q43,"S")</f>
         <v/>
       </c>
-      <c r="T43" s="54">
+      <c r="T43" s="73">
         <f>IF(R43=0,"",S43/R43)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="33">
-      <c r="A44" s="51" t="n"/>
+      <c r="A44" s="71" t="n"/>
       <c r="B44" s="52" t="n"/>
       <c r="C44" s="52" t="n"/>
       <c r="D44" s="52" t="n"/>
@@ -3115,21 +3288,21 @@
       <c r="O44" s="53" t="n"/>
       <c r="P44" s="53" t="n"/>
       <c r="Q44" s="53" t="n"/>
-      <c r="R44" s="43">
+      <c r="R44" s="72">
         <f>COUNTIF(F44:Q44,"R")+COUNTIF(F44:Q44,"S")+COUNTIF(F44:Q44,"T")</f>
         <v/>
       </c>
-      <c r="S44" s="43">
+      <c r="S44" s="72">
         <f>COUNTIF(F44:Q44,"S")</f>
         <v/>
       </c>
-      <c r="T44" s="54">
+      <c r="T44" s="73">
         <f>IF(R44=0,"",S44/R44)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="33">
-      <c r="A45" s="51" t="n"/>
+      <c r="A45" s="71" t="n"/>
       <c r="B45" s="52" t="n"/>
       <c r="C45" s="52" t="n"/>
       <c r="D45" s="52" t="n"/>
@@ -3146,26 +3319,66 @@
       <c r="O45" s="53" t="n"/>
       <c r="P45" s="53" t="n"/>
       <c r="Q45" s="53" t="n"/>
-      <c r="R45" s="43">
+      <c r="R45" s="72">
         <f>COUNTIF(F45:Q45,"R")+COUNTIF(F45:Q45,"S")+COUNTIF(F45:Q45,"T")</f>
         <v/>
       </c>
-      <c r="S45" s="43">
+      <c r="S45" s="72">
         <f>COUNTIF(F45:Q45,"S")</f>
         <v/>
       </c>
-      <c r="T45" s="54">
+      <c r="T45" s="73">
         <f>IF(R45=0,"",S45/R45)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="33">
-      <c r="B47" s="55" t="inlineStr">
+    <row r="46" s="33">
+      <c r="A46" s="70" t="n"/>
+      <c r="B46" s="70" t="n"/>
+      <c r="C46" s="70" t="n"/>
+      <c r="D46" s="70" t="n"/>
+      <c r="E46" s="70" t="n"/>
+      <c r="F46" s="70" t="n"/>
+      <c r="G46" s="70" t="n"/>
+      <c r="H46" s="70" t="n"/>
+      <c r="I46" s="70" t="n"/>
+      <c r="J46" s="70" t="n"/>
+      <c r="K46" s="70" t="n"/>
+      <c r="L46" s="70" t="n"/>
+      <c r="M46" s="70" t="n"/>
+      <c r="N46" s="70" t="n"/>
+      <c r="O46" s="70" t="n"/>
+      <c r="P46" s="70" t="n"/>
+      <c r="Q46" s="70" t="n"/>
+      <c r="R46" s="70" t="n"/>
+      <c r="S46" s="70" t="n"/>
+      <c r="T46" s="70" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1" s="33">
+      <c r="A47" s="70" t="n"/>
+      <c r="B47" s="74" t="inlineStr">
         <is>
           <t>Kepatuhan PM keseluruhan</t>
         </is>
       </c>
-      <c r="T47" s="56">
+      <c r="C47" s="70" t="n"/>
+      <c r="D47" s="70" t="n"/>
+      <c r="E47" s="70" t="n"/>
+      <c r="F47" s="70" t="n"/>
+      <c r="G47" s="70" t="n"/>
+      <c r="H47" s="70" t="n"/>
+      <c r="I47" s="70" t="n"/>
+      <c r="J47" s="70" t="n"/>
+      <c r="K47" s="70" t="n"/>
+      <c r="L47" s="70" t="n"/>
+      <c r="M47" s="70" t="n"/>
+      <c r="N47" s="70" t="n"/>
+      <c r="O47" s="70" t="n"/>
+      <c r="P47" s="70" t="n"/>
+      <c r="Q47" s="70" t="n"/>
+      <c r="R47" s="70" t="n"/>
+      <c r="S47" s="70" t="n"/>
+      <c r="T47" s="75">
         <f>IF(SUM(R6:R45)=0,"",SUM(S6:S45)/SUM(R6:R45))</f>
         <v/>
       </c>
@@ -3187,7 +3400,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -3202,15 +3415,19 @@
   <cols>
     <col width="13" customWidth="1" style="32" min="1" max="1"/>
     <col width="11" customWidth="1" style="32" min="2" max="2"/>
-    <col width="7" customWidth="1" style="32" min="3" max="3"/>
+    <col width="8" customWidth="1" style="32" min="3" max="3"/>
     <col width="20" customWidth="1" style="32" min="4" max="4"/>
     <col width="14" customWidth="1" style="32" min="5" max="6"/>
+    <col width="13" customWidth="1" style="33" min="6" max="6"/>
     <col width="30" customWidth="1" style="32" min="7" max="7"/>
     <col width="26" customWidth="1" style="32" min="8" max="9"/>
+    <col width="13" customWidth="1" style="33" min="9" max="9"/>
     <col width="12" customWidth="1" style="32" min="10" max="10"/>
     <col width="15" customWidth="1" style="32" min="11" max="12"/>
-    <col width="9" customWidth="1" style="32" min="13" max="13"/>
+    <col width="13" customWidth="1" style="33" min="12" max="12"/>
+    <col width="11" customWidth="1" style="32" min="13" max="13"/>
     <col width="14" customWidth="1" style="32" min="14" max="15"/>
+    <col width="18" customWidth="1" style="33" min="15" max="15"/>
     <col width="18" customWidth="1" style="32" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -6506,6 +6723,6 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>